--- a/excel_files/3.9.2.xlsx
+++ b/excel_files/3.9.2.xlsx
@@ -1,10 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29628"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBBF755B-DDB8-4727-BED3-B0622BF39C8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-15" yWindow="-15" windowWidth="10245" windowHeight="8145"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -14,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="40">
   <si>
     <t>Кыргызская Республика</t>
   </si>
@@ -139,7 +140,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="_-* #,##0.00_р_._-;\-* #,##0.00_р_._-;_-* &quot;-&quot;??_р_._-;_-@_-"/>
     <numFmt numFmtId="165" formatCode="0.0"/>
@@ -321,25 +322,21 @@
     <xf numFmtId="166" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -351,86 +348,84 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="11" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="11" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="11" fillId="0" borderId="3" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="18">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
-    <cellStyle name="Обычный 10" xfId="5"/>
-    <cellStyle name="Обычный 2" xfId="3"/>
-    <cellStyle name="Обычный 2 2" xfId="6"/>
-    <cellStyle name="Обычный 2 3" xfId="7"/>
-    <cellStyle name="Обычный 3" xfId="8"/>
-    <cellStyle name="Обычный 3 2" xfId="9"/>
-    <cellStyle name="Обычный 4" xfId="1"/>
-    <cellStyle name="Обычный 5" xfId="2"/>
-    <cellStyle name="Обычный 6" xfId="4"/>
-    <cellStyle name="Обычный 8" xfId="10"/>
-    <cellStyle name="Обычный 9" xfId="11"/>
-    <cellStyle name="Пояснение 2" xfId="12"/>
-    <cellStyle name="Процентный 2" xfId="13"/>
-    <cellStyle name="Процентный 3" xfId="14"/>
-    <cellStyle name="Стиль 1" xfId="15"/>
-    <cellStyle name="Финансовый 2" xfId="16"/>
-    <cellStyle name="Финансовый 3" xfId="17"/>
+    <cellStyle name="Обычный 10" xfId="5" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
+    <cellStyle name="Обычный 2" xfId="3" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
+    <cellStyle name="Обычный 2 2" xfId="6" xr:uid="{00000000-0005-0000-0000-000003000000}"/>
+    <cellStyle name="Обычный 2 3" xfId="7" xr:uid="{00000000-0005-0000-0000-000004000000}"/>
+    <cellStyle name="Обычный 3" xfId="8" xr:uid="{00000000-0005-0000-0000-000005000000}"/>
+    <cellStyle name="Обычный 3 2" xfId="9" xr:uid="{00000000-0005-0000-0000-000006000000}"/>
+    <cellStyle name="Обычный 4" xfId="1" xr:uid="{00000000-0005-0000-0000-000007000000}"/>
+    <cellStyle name="Обычный 5" xfId="2" xr:uid="{00000000-0005-0000-0000-000008000000}"/>
+    <cellStyle name="Обычный 6" xfId="4" xr:uid="{00000000-0005-0000-0000-000009000000}"/>
+    <cellStyle name="Обычный 8" xfId="10" xr:uid="{00000000-0005-0000-0000-00000A000000}"/>
+    <cellStyle name="Обычный 9" xfId="11" xr:uid="{00000000-0005-0000-0000-00000B000000}"/>
+    <cellStyle name="Пояснение 2" xfId="12" xr:uid="{00000000-0005-0000-0000-00000C000000}"/>
+    <cellStyle name="Процентный 2" xfId="13" xr:uid="{00000000-0005-0000-0000-00000D000000}"/>
+    <cellStyle name="Процентный 3" xfId="14" xr:uid="{00000000-0005-0000-0000-00000E000000}"/>
+    <cellStyle name="Стиль 1" xfId="15" xr:uid="{00000000-0005-0000-0000-00000F000000}"/>
+    <cellStyle name="Финансовый 2" xfId="16" xr:uid="{00000000-0005-0000-0000-000010000000}"/>
+    <cellStyle name="Финансовый 3" xfId="17" xr:uid="{00000000-0005-0000-0000-000011000000}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9"/>
@@ -446,9 +441,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Тема Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Стандартная">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -486,9 +481,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Стандартная">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -523,7 +518,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -558,7 +553,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Стандартная">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -731,768 +726,791 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:T15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:U15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="3" width="37.140625" customWidth="1"/>
     <col min="4" max="20" width="8.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" ht="72" customHeight="1">
-      <c r="A1" s="30" t="s">
+    <row r="1" spans="1:21" ht="72" customHeight="1">
+      <c r="A1" s="23" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B1" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="C1" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-      <c r="H1" s="1"/>
-      <c r="I1" s="1"/>
-      <c r="J1" s="1"/>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-      <c r="N1" s="1"/>
     </row>
-    <row r="2" spans="1:20">
-      <c r="A2" s="13" t="s">
+    <row r="2" spans="1:21">
+      <c r="A2" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="B2" s="13" t="s">
+      <c r="B2" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="13" t="s">
+      <c r="C2" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
-      <c r="H2" s="2"/>
-      <c r="I2" s="2"/>
-      <c r="J2" s="2"/>
-      <c r="K2" s="2"/>
-      <c r="L2" s="3"/>
-      <c r="M2" s="2"/>
-      <c r="N2" s="2"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1"/>
+      <c r="K2" s="1"/>
+      <c r="L2" s="1"/>
+      <c r="M2" s="1"/>
+      <c r="N2" s="1"/>
     </row>
-    <row r="3" spans="1:20" ht="15.75" thickBot="1">
-      <c r="A3" s="7"/>
-      <c r="B3" s="7"/>
-      <c r="C3" s="7"/>
-      <c r="D3" s="2"/>
-      <c r="E3" s="2"/>
-      <c r="F3" s="2"/>
-      <c r="G3" s="2"/>
-      <c r="H3" s="2"/>
-      <c r="I3" s="2"/>
-      <c r="J3" s="2"/>
-      <c r="K3" s="2"/>
-      <c r="L3" s="3"/>
-      <c r="M3" s="2"/>
-      <c r="N3" s="2"/>
+    <row r="3" spans="1:21" ht="15.75" thickBot="1">
+      <c r="A3" s="5"/>
+      <c r="B3" s="5"/>
+      <c r="C3" s="5"/>
+      <c r="D3" s="1"/>
+      <c r="E3" s="1"/>
+      <c r="F3" s="1"/>
+      <c r="G3" s="1"/>
+      <c r="H3" s="1"/>
+      <c r="I3" s="1"/>
+      <c r="J3" s="1"/>
+      <c r="K3" s="1"/>
+      <c r="L3" s="1"/>
+      <c r="M3" s="1"/>
+      <c r="N3" s="1"/>
+      <c r="U3" s="24"/>
     </row>
-    <row r="4" spans="1:20" ht="15.75" thickBot="1">
-      <c r="A4" s="8" t="s">
+    <row r="4" spans="1:21" ht="15.75" thickBot="1">
+      <c r="A4" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="B4" s="14" t="s">
+      <c r="B4" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="15" t="s">
+      <c r="C4" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="D4" s="22">
+      <c r="D4" s="16">
         <v>2007</v>
       </c>
-      <c r="E4" s="22">
+      <c r="E4" s="16">
         <v>2008</v>
       </c>
-      <c r="F4" s="22">
+      <c r="F4" s="16">
         <v>2009</v>
       </c>
-      <c r="G4" s="22">
+      <c r="G4" s="16">
         <v>2010</v>
       </c>
-      <c r="H4" s="22">
+      <c r="H4" s="16">
         <v>2011</v>
       </c>
-      <c r="I4" s="23">
+      <c r="I4" s="16">
         <v>2012</v>
       </c>
-      <c r="J4" s="23">
+      <c r="J4" s="16">
         <v>2013</v>
       </c>
-      <c r="K4" s="23">
+      <c r="K4" s="16">
         <v>2014</v>
       </c>
-      <c r="L4" s="22">
+      <c r="L4" s="16">
         <v>2015</v>
       </c>
-      <c r="M4" s="23">
+      <c r="M4" s="16">
         <v>2016</v>
       </c>
-      <c r="N4" s="23">
+      <c r="N4" s="16">
         <v>2017</v>
       </c>
-      <c r="O4" s="23">
+      <c r="O4" s="16">
         <v>2018</v>
       </c>
-      <c r="P4" s="23">
+      <c r="P4" s="16">
         <v>2019</v>
       </c>
-      <c r="Q4" s="23">
+      <c r="Q4" s="16">
         <v>2020</v>
       </c>
-      <c r="R4" s="23">
+      <c r="R4" s="16">
         <v>2021</v>
       </c>
-      <c r="S4" s="23">
+      <c r="S4" s="16">
         <v>2022</v>
       </c>
-      <c r="T4" s="23">
+      <c r="T4" s="16">
         <v>2023</v>
       </c>
+      <c r="U4" s="25">
+        <v>2024</v>
+      </c>
     </row>
-    <row r="5" spans="1:20" ht="17.25" customHeight="1">
-      <c r="A5" s="9" t="s">
+    <row r="5" spans="1:21" ht="17.25" customHeight="1">
+      <c r="A5" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="B5" s="16" t="s">
+      <c r="B5" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="C5" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="D5" s="24">
+      <c r="D5" s="17">
         <v>4.3</v>
       </c>
-      <c r="E5" s="24">
+      <c r="E5" s="17">
         <v>4</v>
       </c>
-      <c r="F5" s="24">
+      <c r="F5" s="17">
         <v>3.2</v>
       </c>
-      <c r="G5" s="24">
+      <c r="G5" s="17">
         <v>2.5</v>
       </c>
-      <c r="H5" s="24">
+      <c r="H5" s="17">
         <v>3.2</v>
       </c>
-      <c r="I5" s="24">
+      <c r="I5" s="17">
         <v>2.8</v>
       </c>
-      <c r="J5" s="24">
+      <c r="J5" s="17">
         <v>1.8</v>
       </c>
-      <c r="K5" s="24">
+      <c r="K5" s="17">
         <v>1.7</v>
       </c>
-      <c r="L5" s="24">
+      <c r="L5" s="17">
         <v>1.9</v>
       </c>
-      <c r="M5" s="24">
+      <c r="M5" s="17">
         <v>1.3</v>
       </c>
-      <c r="N5" s="27">
+      <c r="N5" s="20">
         <v>1.2</v>
       </c>
-      <c r="O5" s="27">
+      <c r="O5" s="20">
         <v>0.8</v>
       </c>
-      <c r="P5" s="27">
+      <c r="P5" s="20">
         <v>0.9</v>
       </c>
-      <c r="Q5" s="27">
+      <c r="Q5" s="20">
         <v>0.1</v>
       </c>
-      <c r="R5" s="27">
+      <c r="R5" s="20">
         <v>1</v>
       </c>
-      <c r="S5" s="27">
+      <c r="S5" s="20">
         <v>1.2</v>
       </c>
-      <c r="T5" s="27">
+      <c r="T5" s="20">
         <v>0.7</v>
       </c>
+      <c r="U5" s="26">
+        <v>0.3</v>
+      </c>
     </row>
-    <row r="6" spans="1:20" ht="15" customHeight="1">
-      <c r="A6" s="10" t="s">
+    <row r="6" spans="1:21" ht="15" customHeight="1">
+      <c r="A6" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="B6" s="17" t="s">
+      <c r="B6" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="C6" s="18" t="s">
+      <c r="C6" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="D6" s="25">
+      <c r="D6" s="18">
         <v>11.4</v>
       </c>
-      <c r="E6" s="25">
+      <c r="E6" s="18">
         <v>11.5</v>
       </c>
-      <c r="F6" s="25">
+      <c r="F6" s="18">
         <v>8.1</v>
       </c>
-      <c r="G6" s="25">
+      <c r="G6" s="18">
         <v>7.8</v>
       </c>
-      <c r="H6" s="25">
+      <c r="H6" s="18">
         <v>11</v>
       </c>
-      <c r="I6" s="25">
+      <c r="I6" s="18">
         <v>5.3</v>
       </c>
-      <c r="J6" s="25">
+      <c r="J6" s="18">
         <v>6.7</v>
       </c>
-      <c r="K6" s="25">
+      <c r="K6" s="18">
         <v>7.6</v>
       </c>
-      <c r="L6" s="25">
+      <c r="L6" s="18">
         <v>5.3</v>
       </c>
-      <c r="M6" s="25">
+      <c r="M6" s="18">
         <v>3.6</v>
       </c>
-      <c r="N6" s="28">
+      <c r="N6" s="21">
         <v>3.1</v>
       </c>
-      <c r="O6" s="28">
+      <c r="O6" s="21">
         <v>1.5</v>
       </c>
-      <c r="P6" s="28">
+      <c r="P6" s="21">
         <v>2.1</v>
       </c>
-      <c r="Q6" s="25">
+      <c r="Q6" s="18">
         <v>0.2</v>
       </c>
-      <c r="R6" s="28">
+      <c r="R6" s="21">
         <v>2.2000000000000002</v>
       </c>
-      <c r="S6" s="28">
+      <c r="S6" s="21">
         <v>2.7</v>
       </c>
-      <c r="T6" s="28">
+      <c r="T6" s="21">
         <v>0.7</v>
       </c>
+      <c r="U6" s="27">
+        <v>0.5</v>
+      </c>
     </row>
-    <row r="7" spans="1:20" ht="15" customHeight="1">
-      <c r="A7" s="10" t="s">
+    <row r="7" spans="1:21" ht="15" customHeight="1">
+      <c r="A7" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="B7" s="17" t="s">
+      <c r="B7" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="C7" s="5" t="s">
+      <c r="C7" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="D7" s="25">
+      <c r="D7" s="18">
         <v>4.0999999999999996</v>
       </c>
-      <c r="E7" s="25">
+      <c r="E7" s="18">
         <v>3.5</v>
       </c>
-      <c r="F7" s="25">
+      <c r="F7" s="18">
         <v>3.5</v>
       </c>
-      <c r="G7" s="25">
+      <c r="G7" s="18">
         <v>2.8</v>
       </c>
-      <c r="H7" s="25">
+      <c r="H7" s="18">
         <v>2.4</v>
       </c>
-      <c r="I7" s="25">
+      <c r="I7" s="18">
         <v>2.2999999999999998</v>
       </c>
-      <c r="J7" s="25">
+      <c r="J7" s="18">
         <v>1.5</v>
       </c>
-      <c r="K7" s="25">
+      <c r="K7" s="18">
         <v>1.4</v>
       </c>
-      <c r="L7" s="25">
+      <c r="L7" s="18">
         <v>2.2000000000000002</v>
       </c>
-      <c r="M7" s="25">
+      <c r="M7" s="18">
         <v>0.9</v>
       </c>
-      <c r="N7" s="28">
+      <c r="N7" s="21">
         <v>1.3</v>
       </c>
-      <c r="O7" s="28">
+      <c r="O7" s="21">
         <v>0.7</v>
       </c>
-      <c r="P7" s="28">
+      <c r="P7" s="21">
         <v>0.4</v>
       </c>
-      <c r="Q7" s="25" t="s">
+      <c r="Q7" s="18" t="s">
         <v>36</v>
       </c>
-      <c r="R7" s="28">
+      <c r="R7" s="21">
         <v>1.7</v>
       </c>
-      <c r="S7" s="28">
+      <c r="S7" s="21">
         <v>0.9</v>
       </c>
-      <c r="T7" s="28">
+      <c r="T7" s="21">
         <v>1.1000000000000001</v>
       </c>
+      <c r="U7" s="27">
+        <v>0.3</v>
+      </c>
     </row>
-    <row r="8" spans="1:20" ht="15" customHeight="1">
-      <c r="A8" s="10" t="s">
+    <row r="8" spans="1:21" ht="15" customHeight="1">
+      <c r="A8" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="B8" s="17" t="s">
+      <c r="B8" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="C8" s="5" t="s">
+      <c r="C8" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="D8" s="25">
+      <c r="D8" s="18">
         <v>3.5</v>
       </c>
-      <c r="E8" s="25">
+      <c r="E8" s="18">
         <v>3</v>
       </c>
-      <c r="F8" s="25">
+      <c r="F8" s="18">
         <v>1.1000000000000001</v>
       </c>
-      <c r="G8" s="25">
+      <c r="G8" s="18">
         <v>0.9</v>
       </c>
-      <c r="H8" s="25">
+      <c r="H8" s="18">
         <v>2.9</v>
       </c>
-      <c r="I8" s="25">
+      <c r="I8" s="18">
         <v>1.8</v>
       </c>
-      <c r="J8" s="25">
+      <c r="J8" s="18">
         <v>0.9</v>
       </c>
-      <c r="K8" s="25">
+      <c r="K8" s="18">
         <v>0.9</v>
       </c>
-      <c r="L8" s="25">
+      <c r="L8" s="18">
         <v>1.1000000000000001</v>
       </c>
-      <c r="M8" s="25">
+      <c r="M8" s="18">
         <v>0.6</v>
       </c>
-      <c r="N8" s="28">
+      <c r="N8" s="21">
         <v>0.6</v>
       </c>
-      <c r="O8" s="28">
+      <c r="O8" s="21">
         <v>0.6</v>
       </c>
-      <c r="P8" s="28">
+      <c r="P8" s="21">
         <v>0.6</v>
       </c>
-      <c r="Q8" s="25">
+      <c r="Q8" s="18">
         <v>0.2</v>
       </c>
-      <c r="R8" s="28" t="s">
+      <c r="R8" s="21" t="s">
         <v>36</v>
       </c>
-      <c r="S8" s="28">
+      <c r="S8" s="21">
         <v>0.4</v>
       </c>
-      <c r="T8" s="28" t="s">
+      <c r="T8" s="21" t="s">
         <v>36</v>
       </c>
+      <c r="U8" s="27" t="s">
+        <v>36</v>
+      </c>
     </row>
-    <row r="9" spans="1:20" ht="15" customHeight="1">
-      <c r="A9" s="10" t="s">
+    <row r="9" spans="1:21" ht="15" customHeight="1">
+      <c r="A9" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="B9" s="17" t="s">
+      <c r="B9" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="C9" s="5" t="s">
+      <c r="C9" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="D9" s="25">
+      <c r="D9" s="18">
         <v>5.0999999999999996</v>
       </c>
-      <c r="E9" s="25">
+      <c r="E9" s="18">
         <v>3.1</v>
       </c>
-      <c r="F9" s="25">
+      <c r="F9" s="18">
         <v>3.1</v>
       </c>
-      <c r="G9" s="25">
+      <c r="G9" s="18">
         <v>3.1</v>
       </c>
-      <c r="H9" s="25">
+      <c r="H9" s="18">
         <v>4.2</v>
       </c>
-      <c r="I9" s="25">
+      <c r="I9" s="18">
         <v>2.6</v>
       </c>
-      <c r="J9" s="25">
+      <c r="J9" s="18">
         <v>1.5</v>
       </c>
-      <c r="K9" s="25">
+      <c r="K9" s="18">
         <v>1.5</v>
       </c>
-      <c r="L9" s="25">
+      <c r="L9" s="18">
         <v>2.2000000000000002</v>
       </c>
-      <c r="M9" s="25">
+      <c r="M9" s="18">
         <v>0.7</v>
       </c>
-      <c r="N9" s="28">
+      <c r="N9" s="21">
         <v>1.4</v>
       </c>
-      <c r="O9" s="28">
+      <c r="O9" s="21">
         <v>1.1000000000000001</v>
       </c>
-      <c r="P9" s="28">
+      <c r="P9" s="21">
         <v>1.4</v>
       </c>
-      <c r="Q9" s="25" t="s">
+      <c r="Q9" s="18" t="s">
         <v>36</v>
       </c>
-      <c r="R9" s="28">
+      <c r="R9" s="21">
         <v>0.3</v>
       </c>
-      <c r="S9" s="28">
+      <c r="S9" s="21">
         <v>0.7</v>
       </c>
-      <c r="T9" s="28">
+      <c r="T9" s="21">
         <v>1.3</v>
       </c>
+      <c r="U9" s="27" t="s">
+        <v>36</v>
+      </c>
     </row>
-    <row r="10" spans="1:20" ht="15" customHeight="1">
-      <c r="A10" s="10" t="s">
+    <row r="10" spans="1:21" ht="15" customHeight="1">
+      <c r="A10" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="B10" s="17" t="s">
+      <c r="B10" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="C10" s="5" t="s">
+      <c r="C10" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D10" s="25">
+      <c r="D10" s="18">
         <v>6.2</v>
       </c>
-      <c r="E10" s="25">
+      <c r="E10" s="18">
         <v>6.9</v>
       </c>
-      <c r="F10" s="25">
+      <c r="F10" s="18">
         <v>5.4</v>
       </c>
-      <c r="G10" s="25">
+      <c r="G10" s="18">
         <v>3.2</v>
       </c>
-      <c r="H10" s="25">
+      <c r="H10" s="18">
         <v>3.4</v>
       </c>
-      <c r="I10" s="25">
+      <c r="I10" s="18">
         <v>5.3</v>
       </c>
-      <c r="J10" s="25">
+      <c r="J10" s="18">
         <v>2.2000000000000002</v>
       </c>
-      <c r="K10" s="25">
+      <c r="K10" s="18">
         <v>2.2000000000000002</v>
       </c>
-      <c r="L10" s="25">
+      <c r="L10" s="18">
         <v>2.6</v>
       </c>
-      <c r="M10" s="25">
+      <c r="M10" s="18">
         <v>2.2000000000000002</v>
       </c>
-      <c r="N10" s="28">
+      <c r="N10" s="21">
         <v>1.6</v>
       </c>
-      <c r="O10" s="28">
+      <c r="O10" s="21">
         <v>1.5</v>
       </c>
-      <c r="P10" s="28">
+      <c r="P10" s="21">
         <v>1.3</v>
       </c>
-      <c r="Q10" s="25">
+      <c r="Q10" s="18">
         <v>0.1</v>
       </c>
-      <c r="R10" s="28">
+      <c r="R10" s="21">
         <v>1.1000000000000001</v>
       </c>
-      <c r="S10" s="28">
+      <c r="S10" s="21">
         <v>0.9</v>
       </c>
-      <c r="T10" s="28">
+      <c r="T10" s="21">
         <v>0.9</v>
       </c>
+      <c r="U10" s="27">
+        <v>0.5</v>
+      </c>
     </row>
-    <row r="11" spans="1:20" ht="15" customHeight="1">
-      <c r="A11" s="10" t="s">
+    <row r="11" spans="1:21" ht="15" customHeight="1">
+      <c r="A11" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="B11" s="17" t="s">
+      <c r="B11" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="C11" s="5" t="s">
+      <c r="C11" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="D11" s="25">
+      <c r="D11" s="18">
         <v>4.9000000000000004</v>
       </c>
-      <c r="E11" s="25">
+      <c r="E11" s="18">
         <v>2.7</v>
       </c>
-      <c r="F11" s="25">
+      <c r="F11" s="18">
         <v>4.4000000000000004</v>
       </c>
-      <c r="G11" s="25">
+      <c r="G11" s="18">
         <v>1.7</v>
       </c>
-      <c r="H11" s="25">
+      <c r="H11" s="18">
         <v>4.7</v>
       </c>
-      <c r="I11" s="25">
+      <c r="I11" s="18">
         <v>2.5</v>
       </c>
-      <c r="J11" s="25">
+      <c r="J11" s="18">
         <v>0.8</v>
       </c>
-      <c r="K11" s="25">
+      <c r="K11" s="18">
         <v>1.2</v>
       </c>
-      <c r="L11" s="25">
+      <c r="L11" s="18">
         <v>2.4</v>
       </c>
-      <c r="M11" s="25">
+      <c r="M11" s="18">
         <v>2.4</v>
       </c>
-      <c r="N11" s="28">
+      <c r="N11" s="21">
         <v>0.4</v>
       </c>
-      <c r="O11" s="28">
+      <c r="O11" s="21">
         <v>0.8</v>
       </c>
-      <c r="P11" s="28">
+      <c r="P11" s="21">
         <v>0.4</v>
       </c>
-      <c r="Q11" s="25" t="s">
+      <c r="Q11" s="18" t="s">
         <v>36</v>
       </c>
-      <c r="R11" s="28" t="s">
+      <c r="R11" s="21" t="s">
         <v>36</v>
       </c>
-      <c r="S11" s="28">
+      <c r="S11" s="21">
         <v>1.1000000000000001</v>
       </c>
-      <c r="T11" s="28">
+      <c r="T11" s="21">
         <v>0.4</v>
       </c>
+      <c r="U11" s="27" t="s">
+        <v>36</v>
+      </c>
     </row>
-    <row r="12" spans="1:20" ht="15" customHeight="1">
-      <c r="A12" s="10" t="s">
+    <row r="12" spans="1:21" ht="15" customHeight="1">
+      <c r="A12" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="B12" s="17" t="s">
+      <c r="B12" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="C12" s="5" t="s">
+      <c r="C12" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="D12" s="25">
+      <c r="D12" s="18">
         <v>2</v>
       </c>
-      <c r="E12" s="25">
+      <c r="E12" s="18">
         <v>1.6</v>
       </c>
-      <c r="F12" s="25">
+      <c r="F12" s="18">
         <v>1.5</v>
       </c>
-      <c r="G12" s="25">
+      <c r="G12" s="18">
         <v>1</v>
       </c>
-      <c r="H12" s="25">
+      <c r="H12" s="18">
         <v>2</v>
       </c>
-      <c r="I12" s="25">
+      <c r="I12" s="18">
         <v>2.2000000000000002</v>
       </c>
-      <c r="J12" s="25">
+      <c r="J12" s="18">
         <v>1.2</v>
       </c>
-      <c r="K12" s="25">
+      <c r="K12" s="18">
         <v>0.6</v>
       </c>
-      <c r="L12" s="25">
+      <c r="L12" s="18">
         <v>0.8</v>
       </c>
-      <c r="M12" s="25">
+      <c r="M12" s="18">
         <v>0.7</v>
       </c>
-      <c r="N12" s="28">
+      <c r="N12" s="21">
         <v>0.8</v>
       </c>
-      <c r="O12" s="28">
+      <c r="O12" s="21">
         <v>0.1</v>
       </c>
-      <c r="P12" s="28">
+      <c r="P12" s="21">
         <v>0.7</v>
       </c>
-      <c r="Q12" s="25">
+      <c r="Q12" s="18">
         <v>0.3</v>
       </c>
-      <c r="R12" s="28">
+      <c r="R12" s="21">
         <v>0.9</v>
       </c>
-      <c r="S12" s="28">
+      <c r="S12" s="21">
         <v>2.7</v>
       </c>
-      <c r="T12" s="28">
+      <c r="T12" s="21">
         <v>0.8</v>
       </c>
+      <c r="U12" s="27">
+        <v>0.1</v>
+      </c>
     </row>
-    <row r="13" spans="1:20" ht="15" customHeight="1">
-      <c r="A13" s="11" t="s">
+    <row r="13" spans="1:21" ht="15" customHeight="1">
+      <c r="A13" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="B13" s="17" t="s">
+      <c r="B13" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="C13" s="5" t="s">
+      <c r="C13" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="D13" s="25">
+      <c r="D13" s="18">
         <v>1.5</v>
       </c>
-      <c r="E13" s="25">
+      <c r="E13" s="18">
         <v>1.2</v>
       </c>
-      <c r="F13" s="25">
+      <c r="F13" s="18">
         <v>0.5</v>
       </c>
-      <c r="G13" s="25">
+      <c r="G13" s="18">
         <v>0.8</v>
       </c>
-      <c r="H13" s="25">
+      <c r="H13" s="18">
         <v>1.3</v>
       </c>
-      <c r="I13" s="25">
+      <c r="I13" s="18">
         <v>0.8</v>
       </c>
-      <c r="J13" s="25">
+      <c r="J13" s="18">
         <v>0.8</v>
       </c>
-      <c r="K13" s="25">
+      <c r="K13" s="18">
         <v>0.4</v>
       </c>
-      <c r="L13" s="25">
+      <c r="L13" s="18">
         <v>0.8</v>
       </c>
-      <c r="M13" s="25">
+      <c r="M13" s="18">
         <v>0.6</v>
       </c>
-      <c r="N13" s="28">
+      <c r="N13" s="21">
         <v>0.6</v>
       </c>
-      <c r="O13" s="28">
+      <c r="O13" s="21">
         <v>0.4</v>
       </c>
-      <c r="P13" s="28">
+      <c r="P13" s="21">
         <v>0.7</v>
       </c>
-      <c r="Q13" s="28" t="s">
+      <c r="Q13" s="21" t="s">
         <v>36</v>
       </c>
-      <c r="R13" s="28">
+      <c r="R13" s="21">
         <v>0.4</v>
       </c>
-      <c r="S13" s="28">
+      <c r="S13" s="21">
         <v>0.4</v>
       </c>
-      <c r="T13" s="28">
+      <c r="T13" s="21">
         <v>0.3</v>
       </c>
+      <c r="U13" s="27">
+        <v>0.5</v>
+      </c>
     </row>
-    <row r="14" spans="1:20" ht="15" customHeight="1" thickBot="1">
-      <c r="A14" s="12" t="s">
+    <row r="14" spans="1:21" ht="15" customHeight="1" thickBot="1">
+      <c r="A14" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="B14" s="19" t="s">
+      <c r="B14" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="C14" s="20" t="s">
+      <c r="C14" s="14" t="s">
         <v>31</v>
       </c>
-      <c r="D14" s="26">
+      <c r="D14" s="19">
         <v>0.4</v>
       </c>
-      <c r="E14" s="26">
+      <c r="E14" s="19">
         <v>0.8</v>
       </c>
-      <c r="F14" s="26">
+      <c r="F14" s="19">
         <v>1.5</v>
       </c>
-      <c r="G14" s="26">
+      <c r="G14" s="19">
         <v>1.6</v>
       </c>
-      <c r="H14" s="26">
+      <c r="H14" s="19">
         <v>1.2</v>
       </c>
-      <c r="I14" s="26">
+      <c r="I14" s="19">
         <v>0.8</v>
       </c>
-      <c r="J14" s="26">
+      <c r="J14" s="19">
         <v>1.1000000000000001</v>
       </c>
-      <c r="K14" s="26">
+      <c r="K14" s="19">
         <v>1.1000000000000001</v>
       </c>
-      <c r="L14" s="26">
+      <c r="L14" s="19">
         <v>0.4</v>
       </c>
-      <c r="M14" s="26">
+      <c r="M14" s="19">
         <v>0.4</v>
       </c>
-      <c r="N14" s="29">
+      <c r="N14" s="22">
         <v>0.7</v>
       </c>
-      <c r="O14" s="29">
+      <c r="O14" s="22">
         <v>0.7</v>
       </c>
-      <c r="P14" s="29">
+      <c r="P14" s="22">
         <v>0.7</v>
       </c>
-      <c r="Q14" s="29" t="s">
+      <c r="Q14" s="22" t="s">
         <v>36</v>
       </c>
-      <c r="R14" s="29">
+      <c r="R14" s="22">
         <v>0.6</v>
       </c>
-      <c r="S14" s="29">
+      <c r="S14" s="22">
         <v>0.6</v>
       </c>
-      <c r="T14" s="29" t="s">
+      <c r="T14" s="22" t="s">
         <v>36</v>
       </c>
+      <c r="U14" s="28" t="s">
+        <v>36</v>
+      </c>
     </row>
-    <row r="15" spans="1:20">
-      <c r="D15" s="21"/>
-      <c r="E15" s="21"/>
-      <c r="F15" s="21"/>
-      <c r="G15" s="21"/>
-      <c r="H15" s="21"/>
-      <c r="I15" s="21"/>
-      <c r="J15" s="21"/>
-      <c r="K15" s="21"/>
-      <c r="L15" s="21"/>
-      <c r="M15" s="21"/>
-      <c r="N15" s="21"/>
+    <row r="15" spans="1:21">
+      <c r="D15" s="15"/>
+      <c r="E15" s="15"/>
+      <c r="F15" s="15"/>
+      <c r="G15" s="15"/>
+      <c r="H15" s="15"/>
+      <c r="I15" s="15"/>
+      <c r="J15" s="15"/>
+      <c r="K15" s="15"/>
+      <c r="L15" s="15"/>
+      <c r="M15" s="15"/>
+      <c r="N15" s="15"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
